--- a/artfynd/A 33035-2021 artfynd.xlsx
+++ b/artfynd/A 33035-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33035-2021 artfynd.xlsx
+++ b/artfynd/A 33035-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1072,6 +1072,133 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>62555470</v>
+      </c>
+      <c r="B5" t="n">
+        <v>89745</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5745</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gyllenfingersvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramaria brunneicontusa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>683763</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6685123</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2009-09-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2009-09-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3 ex. under tall och gran, i vegetationsskikt av kranshakmossa, blåsippa, midsommarblomster, stenbär och (skogs)viol, i 70-80 årig barrskog.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>70-80 årig barrskog.</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33035-2021 artfynd.xlsx
+++ b/artfynd/A 33035-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>62555403</v>
       </c>
       <c r="B2" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683932.2911448519</v>
+        <v>683932</v>
       </c>
       <c r="R2" t="n">
-        <v>6685282.801102934</v>
+        <v>6685283</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2009-09-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-09-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -806,59 +791,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62555445</v>
+        <v>97640719</v>
       </c>
       <c r="B3" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>720</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+          <t>Assjö 1, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>683737.6212857984</v>
+        <v>683792</v>
       </c>
       <c r="R3" t="n">
-        <v>6685124.351155246</v>
+        <v>6685049</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,27 +865,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-09-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-09-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ca. 50 ex. i 70-80 årig, örtrik, grandominerad barrskog.</t>
+          <t>Känd växtplats</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,63 +886,57 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Örtrik, grandominerad barrskog.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Elisabet Ottosson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Övervakning Violgubbe C-län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62555470</v>
+        <v>73392632</v>
       </c>
       <c r="B4" t="n">
-        <v>89833</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5745</v>
+        <v>789</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -980,16 +944,17 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+          <t>NO om Assjö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683763</v>
+        <v>683765</v>
       </c>
       <c r="R4" t="n">
-        <v>6685123</v>
+        <v>6685169</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,17 +981,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2009-09-14</t>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2009-09-14</t>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>3 ex. under tall och gran, i vegetationsskikt av kranshakmossa, blåsippa, midsommarblomster, stenbär och (skogs)viol, i 70-80 årig barrskog.</t>
+          <t>cirka</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,32 +1010,2769 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>70-80 årig barrskog.</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Owe Rosengren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Owe Rosengren, Patrick Fritzson, Tor Jonzon, Niklas Hjort</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>866423</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Assjö, NO om, Ö om vägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>683886</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6685266</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>73392254</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91680</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NO om Assjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>683883</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6685250</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Owe Rosengren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Owe Rosengren, Patrick Fritzson, Tor Jonzon, Niklas Hjort</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>62555407</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87309</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>683890</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6685259</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2004-07-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2004-07-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 ex.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik och grandominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Gillis Aronsson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Gillis Aronsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>67719482</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87309</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NO om Assjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>683871</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6685297</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Owe Rosengren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Niklas Hjort, Tor Jonzon, Patrick Fritzson, Owe Rosengren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>67717347</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NO om Assjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>683883</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6685250</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Owe Rosengren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Owe Rosengren, Patrick Fritzson, Tor Jonzon, Niklas Hjort</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>62555443</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>683752</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6685163</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2006-09-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2006-09-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 ex. under äldre gran.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>62555445</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>683738</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6685124</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2009-09-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2009-09-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca. 50 ex. i 70-80 årig, örtrik, grandominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Örtrik, grandominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>67717341</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NO om Assjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>683883</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6685250</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Owe Rosengren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Owe Rosengren, Patrick Fritzson, Tor Jonzon, Niklas Hjort</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>62555470</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91398</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5745</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gyllenfingersvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramaria brunneicontusa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>683763</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6685123</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2009-09-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2009-09-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3 ex. under tall och gran, i vegetationsskikt av kranshakmossa, blåsippa, midsommarblomster, stenbär och (skogs)viol, i 70-80 årig barrskog.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>70-80 årig barrskog.</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>62555495</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92928</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5836</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Guldkremla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Russula aurea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>683747</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6685170</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2004-09-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2004-09-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2 ex.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>67717334</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NO om Assjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>683883</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6685250</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Owe Rosengren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Owe Rosengren, Patrick Fritzson, Tor Jonzon, Niklas Hjort</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2316834</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Assjö, NO om, V om vägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>683805</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6685175</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4051198</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Assjö, NO om, V om vägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>683805</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6685175</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6419160</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106231</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Assjö, NO om, Ö om vägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>683886</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6685266</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>67717419</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NO om Assjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>683871</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6685297</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Owe Rosengren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Owe Rosengren, Patrick Fritzson, Tor Jonzon, Niklas Hjort</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6588197</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Assjö, NO om, Ö om vägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>683886</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6685266</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>56164590</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>683875</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6685140</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2006-09-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2006-09-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca. 50 ex. i ca. 70-årig granskog.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>70-årig, örtrik granskog.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>56164640</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>683899</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6685231</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2009-09-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2009-09-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>3 ex. under gran, i vegetationsskikt av kranshakmossa, blåsippa, stenbär och smultron, i äldre, grandominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>56164675</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>683886</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6685261</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2011-10-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2011-10-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ca. 150 ex. under gran, i vegetationsskikt av kranshakmossa, blåsippa, stenbär och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik och grandominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>67717310</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NO om Assjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>683883</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6685250</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>återfynd. Rikligt</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Owe Rosengren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Owe Rosengren, Patrick Fritzson, Tor Jonzon, Niklas Hjort</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6611599</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91420</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Assjö, NO om, Ö om vägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>683886</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6685266</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>62555464</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91420</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>683888</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6685121</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2004-07-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2004-07-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ca. 20 ex.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Äldre, mossrik granskog.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>62555465</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91420</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>683896</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6685231</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2004-07-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2004-07-28</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ca. 50 ex.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Äldre, mossrik granskog.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>62555468</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91420</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Assjö 2 km NV om Börstil kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>683886</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6685256</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2011-10-06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2011-10-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2 ex. under gran, i vegetationsskikt av kranshakmossa, blåsippa, stenbär och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik och grandominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>73392268</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91420</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>NO om Assjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>683883</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6685250</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Owe Rosengren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Owe Rosengren, Patrick Fritzson, Tor Jonzon, Niklas Hjort</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
